--- a/data/file_generation/reference/data_79/非关键岗位流失情况对比分析报告_res.xlsx
+++ b/data/file_generation/reference/data_79/非关键岗位流失情况对比分析报告_res.xlsx
@@ -1303,26 +1303,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69606841-0B8D-4CBF-BFC4-52D3B3C50B6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16723DFA-8F07-48AD-BF14-C71590211B64}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21441124-B3EE-4DF8-A5A7-BC65FC10C722}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FD82E2-9B93-4393-8CAF-0F0C60C1CFA0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE7D429D-8F16-4AB3-A855-59F5CB3AD490}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{245B696E-D8E6-43D8-99FD-69AB2FD866F8}"/>
 </file>